--- a/database_penyimpanan_aman/database_master_nama_alat.xlsx
+++ b/database_penyimpanan_aman/database_master_nama_alat.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,6 +570,20 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Forklift Caterpiler Kap 5 Ton No FK.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Forklift Caterpiler Kap 5 Ton No FK.05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
